--- a/artfynd/A 36627-2024 artfynd.xlsx
+++ b/artfynd/A 36627-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796564</v>
+        <v>119796565</v>
       </c>
       <c r="B3" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796565</v>
+        <v>119796564</v>
       </c>
       <c r="B4" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 36627-2024 artfynd.xlsx
+++ b/artfynd/A 36627-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119796566</v>
+        <v>119796565</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519748</v>
+        <v>519749</v>
       </c>
       <c r="R2" t="n">
-        <v>6848230</v>
+        <v>6848200</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796565</v>
+        <v>119796564</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796564</v>
+        <v>119796566</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519749</v>
+        <v>519748</v>
       </c>
       <c r="R4" t="n">
-        <v>6848200</v>
+        <v>6848230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820269</v>
+        <v>119820271</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1159,14 +1159,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519711</v>
+        <v>519539</v>
       </c>
       <c r="R6" t="n">
-        <v>6848223</v>
+        <v>6848287</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820271</v>
+        <v>119820269</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1270,14 +1270,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Romberg, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519539</v>
+        <v>519711</v>
       </c>
       <c r="R7" t="n">
-        <v>6848287</v>
+        <v>6848223</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 36627-2024 artfynd.xlsx
+++ b/artfynd/A 36627-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119796565</v>
+        <v>119796564</v>
       </c>
       <c r="B2" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796564</v>
+        <v>119796565</v>
       </c>
       <c r="B3" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820270</v>
+        <v>119820269</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,14 +1048,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Romberg, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519540</v>
+        <v>519711</v>
       </c>
       <c r="R5" t="n">
-        <v>6848288</v>
+        <v>6848223</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820269</v>
+        <v>119820270</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1270,14 +1270,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519711</v>
+        <v>519540</v>
       </c>
       <c r="R7" t="n">
-        <v>6848223</v>
+        <v>6848288</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 36627-2024 artfynd.xlsx
+++ b/artfynd/A 36627-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796565</v>
+        <v>119796566</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519749</v>
+        <v>519748</v>
       </c>
       <c r="R3" t="n">
-        <v>6848200</v>
+        <v>6848230</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796566</v>
+        <v>119796565</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519748</v>
+        <v>519749</v>
       </c>
       <c r="R4" t="n">
-        <v>6848230</v>
+        <v>6848200</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36627-2024 artfynd.xlsx
+++ b/artfynd/A 36627-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796566</v>
+        <v>119796565</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519748</v>
+        <v>519749</v>
       </c>
       <c r="R3" t="n">
-        <v>6848230</v>
+        <v>6848200</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796565</v>
+        <v>119796566</v>
       </c>
       <c r="B4" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519749</v>
+        <v>519748</v>
       </c>
       <c r="R4" t="n">
-        <v>6848200</v>
+        <v>6848230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36627-2024 artfynd.xlsx
+++ b/artfynd/A 36627-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119796564</v>
       </c>
       <c r="B2" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796565</v>
+        <v>119796566</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519749</v>
+        <v>519748</v>
       </c>
       <c r="R3" t="n">
-        <v>6848200</v>
+        <v>6848230</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796566</v>
+        <v>119796565</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519748</v>
+        <v>519749</v>
       </c>
       <c r="R4" t="n">
-        <v>6848230</v>
+        <v>6848200</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820269</v>
+        <v>119820270</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,14 +1048,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519711</v>
+        <v>519540</v>
       </c>
       <c r="R5" t="n">
-        <v>6848223</v>
+        <v>6848288</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>119820271</v>
       </c>
       <c r="B6" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820270</v>
+        <v>119820269</v>
       </c>
       <c r="B7" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1270,14 +1270,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Romberg, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519540</v>
+        <v>519711</v>
       </c>
       <c r="R7" t="n">
-        <v>6848288</v>
+        <v>6848223</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 36627-2024 artfynd.xlsx
+++ b/artfynd/A 36627-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119796564</v>
+        <v>119796566</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519749</v>
+        <v>519748</v>
       </c>
       <c r="R2" t="n">
-        <v>6848200</v>
+        <v>6848230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796566</v>
+        <v>119796565</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519748</v>
+        <v>519749</v>
       </c>
       <c r="R3" t="n">
-        <v>6848230</v>
+        <v>6848200</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796565</v>
+        <v>119796564</v>
       </c>
       <c r="B4" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820270</v>
+        <v>119820271</v>
       </c>
       <c r="B5" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519540</v>
+        <v>519539</v>
       </c>
       <c r="R5" t="n">
-        <v>6848288</v>
+        <v>6848287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820271</v>
+        <v>119820269</v>
       </c>
       <c r="B6" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1159,14 +1159,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Romberg, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519539</v>
+        <v>519711</v>
       </c>
       <c r="R6" t="n">
-        <v>6848287</v>
+        <v>6848223</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820269</v>
+        <v>119820270</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1270,14 +1270,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519711</v>
+        <v>519540</v>
       </c>
       <c r="R7" t="n">
-        <v>6848223</v>
+        <v>6848288</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 36627-2024 artfynd.xlsx
+++ b/artfynd/A 36627-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820271</v>
+        <v>119820269</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,14 +1048,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Romberg, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519539</v>
+        <v>519711</v>
       </c>
       <c r="R5" t="n">
-        <v>6848287</v>
+        <v>6848223</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820269</v>
+        <v>119820270</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1159,14 +1159,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519711</v>
+        <v>519540</v>
       </c>
       <c r="R6" t="n">
-        <v>6848223</v>
+        <v>6848288</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820270</v>
+        <v>119820271</v>
       </c>
       <c r="B7" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519540</v>
+        <v>519539</v>
       </c>
       <c r="R7" t="n">
-        <v>6848288</v>
+        <v>6848287</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 36627-2024 artfynd.xlsx
+++ b/artfynd/A 36627-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>119796566</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796565</v>
+        <v>119820269</v>
       </c>
       <c r="B3" t="n">
-        <v>78279</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519749</v>
+        <v>519711</v>
       </c>
       <c r="R3" t="n">
-        <v>6848200</v>
+        <v>6848223</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -900,12 +890,7 @@
         <v>119796564</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820269</v>
+        <v>119820271</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,14 +1028,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519711</v>
+        <v>519539</v>
       </c>
       <c r="R5" t="n">
-        <v>6848223</v>
+        <v>6848287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820270</v>
+        <v>119796565</v>
       </c>
       <c r="B6" t="n">
-        <v>78279</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,14 +1134,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Romberg, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519540</v>
+        <v>519749</v>
       </c>
       <c r="R6" t="n">
-        <v>6848288</v>
+        <v>6848200</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820271</v>
+        <v>119820270</v>
       </c>
       <c r="B7" t="n">
-        <v>78278</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519539</v>
+        <v>519540</v>
       </c>
       <c r="R7" t="n">
-        <v>6848287</v>
+        <v>6848288</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 36627-2024 artfynd.xlsx
+++ b/artfynd/A 36627-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796566</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820269</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796564</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820271</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796565</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820270</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 36627-2024 artfynd.xlsx
+++ b/artfynd/A 36627-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119796566</v>
+        <v>136042743</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>93353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,17 +715,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519748</v>
+        <v>519478</v>
       </c>
       <c r="R2" t="n">
-        <v>6848230</v>
+        <v>6848249</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,13 +795,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119796566</t>
+          <t>https://artportalen.se/Sighting/136042743</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820269</v>
+        <v>119796566</v>
       </c>
       <c r="B3" t="n">
         <v>79327</v>
@@ -830,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519711</v>
+        <v>519748</v>
       </c>
       <c r="R3" t="n">
-        <v>6848223</v>
+        <v>6848230</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -896,38 +906,38 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119820269</t>
+          <t>https://artportalen.se/Sighting/119796566</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796564</v>
+        <v>119820269</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519749</v>
+        <v>519711</v>
       </c>
       <c r="R4" t="n">
-        <v>6848200</v>
+        <v>6848223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +981,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1007,13 +1017,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119796564</t>
+          <t>https://artportalen.se/Sighting/119820269</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820271</v>
+        <v>119796564</v>
       </c>
       <c r="B5" t="n">
         <v>79084</v>
@@ -1048,14 +1058,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Romberg, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519539</v>
+        <v>519749</v>
       </c>
       <c r="R5" t="n">
-        <v>6848287</v>
+        <v>6848200</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,16 +1128,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119820271</t>
+          <t>https://artportalen.se/Sighting/119796564</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796565</v>
+        <v>119820271</v>
       </c>
       <c r="B6" t="n">
-        <v>79085</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1159,14 +1169,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519749</v>
+        <v>519539</v>
       </c>
       <c r="R6" t="n">
-        <v>6848200</v>
+        <v>6848287</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,13 +1239,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119796565</t>
+          <t>https://artportalen.se/Sighting/119820271</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820270</v>
+        <v>119796565</v>
       </c>
       <c r="B7" t="n">
         <v>79085</v>
@@ -1270,14 +1280,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Romberg, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519540</v>
+        <v>519749</v>
       </c>
       <c r="R7" t="n">
-        <v>6848288</v>
+        <v>6848200</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,6 +1349,117 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796565</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119820270</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Romberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>519540</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6848288</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119820270</t>
         </is>
@@ -1352,6 +1473,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
